--- a/filtered_df_lucas0.xlsx
+++ b/filtered_df_lucas0.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE7"/>
+  <dimension ref="A1:CE12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -846,13 +846,13 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B2" t="n">
-        <v>1908613</v>
+        <v>1908321</v>
       </c>
       <c r="C2" t="n">
-        <v>454349</v>
+        <v>363718</v>
       </c>
       <c r="D2" t="n">
         <v>27</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rocco Vata</t>
+          <t>Edo Kayembe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -873,17 +873,17 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6.12</v>
+        <v>6.06</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>100</v>
       </c>
-      <c r="K2" t="n">
-        <v>50</v>
-      </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
@@ -891,19 +891,19 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -924,13 +924,13 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -954,56 +954,56 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="n">
         <v>2</v>
       </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ2" t="n">
         <v>1</v>
       </c>
@@ -1014,10 +1014,10 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1026,16 +1026,16 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
         <v>0</v>
@@ -1062,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BU2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1100,22 +1100,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>Swansea</t>
+          <t>Charlton</t>
         </is>
       </c>
       <c r="CE2" s="2" t="n">
-        <v>45892</v>
+        <v>45878</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B3" t="n">
-        <v>1908412</v>
+        <v>1908612</v>
       </c>
       <c r="C3" t="n">
-        <v>454349</v>
+        <v>363718</v>
       </c>
       <c r="D3" t="n">
         <v>27</v>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rocco Vata</t>
+          <t>Edo Kayembe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1136,16 +1136,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6.69</v>
+        <v>6.59</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>72.22</v>
+        <v>82.14</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1154,13 +1154,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1175,25 +1175,25 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
         <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -1202,10 +1202,10 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1217,37 +1217,37 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT3" t="n">
         <v>0</v>
@@ -1259,13 +1259,13 @@
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="AX3" t="n">
         <v>1</v>
       </c>
       <c r="AY3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ3" t="n">
         <v>1</v>
@@ -1274,83 +1274,83 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE3" t="n">
         <v>4</v>
       </c>
-      <c r="BE3" t="n">
-        <v>1</v>
-      </c>
       <c r="BF3" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
       <c r="BG3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0.14415</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA3" t="n">
         <v>4</v>
       </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>100</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>1</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
           <t>2025-2026</t>
@@ -1363,22 +1363,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>QPR</t>
         </is>
       </c>
       <c r="CE3" s="2" t="n">
-        <v>45899</v>
+        <v>45885</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B4" t="n">
-        <v>1908367</v>
+        <v>1908613</v>
       </c>
       <c r="C4" t="n">
-        <v>454349</v>
+        <v>363718</v>
       </c>
       <c r="D4" t="n">
         <v>27</v>
@@ -1390,37 +1390,37 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rocco Vata</t>
+          <t>Edo Kayembe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6.25</v>
+        <v>5.99</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>77.78</v>
+        <v>65.22</v>
       </c>
       <c r="L4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1429,151 +1429,151 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
         <v>3</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5</v>
       </c>
-      <c r="Z4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="n">
+      <c r="BD4" t="n">
         <v>2</v>
       </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3</v>
-      </c>
       <c r="BE4" t="n">
         <v>1</v>
       </c>
       <c r="BF4" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="BG4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
         <v>3</v>
       </c>
       <c r="BK4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BL4" t="n">
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="BO4" t="n">
         <v>0</v>
@@ -1588,19 +1588,19 @@
         <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>80</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="BT4" t="n">
         <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="BV4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="BX4" t="n">
         <v>0</v>
@@ -1609,10 +1609,10 @@
         <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CA4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
@@ -1626,22 +1626,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>Blackburn</t>
+          <t>Swansea</t>
         </is>
       </c>
       <c r="CE4" s="2" t="n">
-        <v>45913</v>
+        <v>45892</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B5" t="n">
-        <v>1908363</v>
+        <v>1908412</v>
       </c>
       <c r="C5" t="n">
-        <v>454349</v>
+        <v>363718</v>
       </c>
       <c r="D5" t="n">
         <v>27</v>
@@ -1653,16 +1653,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rocco Vata</t>
+          <t>Edo Kayembe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5.98</v>
+        <v>5.93</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>50</v>
+        <v>78.12</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1680,43 +1680,43 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
+        <v>22</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
         <v>3</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1</v>
-      </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1725,13 +1725,13 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1743,79 +1743,79 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
         <v>2</v>
       </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1</v>
-      </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BG5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -1824,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
@@ -1833,7 +1833,7 @@
         <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
@@ -1851,10 +1851,10 @@
         <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>50</v>
+        <v>77.3</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BU5" t="n">
         <v>0</v>
@@ -1875,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
@@ -1889,22 +1889,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="CE5" s="2" t="n">
-        <v>45922</v>
+        <v>45899</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B6" t="n">
-        <v>1908421</v>
+        <v>1908367</v>
       </c>
       <c r="C6" t="n">
-        <v>454349</v>
+        <v>363718</v>
       </c>
       <c r="D6" t="n">
         <v>27</v>
@@ -1916,34 +1916,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rocco Vata</t>
+          <t>Edo Kayembe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>7.18</v>
+        <v>6.01</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>63.64</v>
+        <v>91.67</v>
       </c>
       <c r="L6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1961,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1970,28 +1970,28 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -2006,139 +2006,139 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AJ6" t="n">
         <v>2</v>
       </c>
       <c r="AK6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE6" t="n">
         <v>3</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BG6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BK6" t="n">
         <v>2</v>
       </c>
       <c r="BL6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.151</v>
+        <v>0</v>
       </c>
       <c r="BN6" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.13955</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>63.6</v>
+        <v>87.5</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BZ6" t="n">
         <v>2</v>
       </c>
       <c r="CA6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
@@ -2152,22 +2152,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Blackburn</t>
         </is>
       </c>
       <c r="CE6" s="2" t="n">
-        <v>45931</v>
+        <v>45913</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
-        <v>1908457</v>
+        <v>1908363</v>
       </c>
       <c r="C7" t="n">
-        <v>454349</v>
+        <v>363718</v>
       </c>
       <c r="D7" t="n">
         <v>27</v>
@@ -2179,25 +2179,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rocco Vata</t>
+          <t>Edo Kayembe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6.43</v>
+        <v>6.12</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>66.67</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>64.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="L7" t="n">
         <v>100</v>
@@ -2206,13 +2206,13 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2239,151 +2239,151 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY7" t="n">
         <v>2</v>
       </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
+      <c r="AZ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>18</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
         <v>15</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>25</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>13</v>
-      </c>
       <c r="BO7" t="n">
-        <v>0.20355</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
         <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>68.2</v>
+        <v>100</v>
       </c>
       <c r="BT7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="BV7" t="n">
         <v>100</v>
@@ -2392,34 +2392,1349 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="CE7" s="2" t="n">
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1908607</v>
+      </c>
+      <c r="C8" t="n">
+        <v>363718</v>
+      </c>
+      <c r="D8" t="n">
+        <v>27</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Edo Kayembe</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.61</v>
+      </c>
+      <c r="L8" t="n">
         <v>100</v>
       </c>
-      <c r="BZ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CA7" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>46</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>45</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>64</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
         <v>8</v>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>26</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>28</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0.01785</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>75</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>50</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>3</v>
+      </c>
+      <c r="CB8" t="inlineStr">
         <is>
           <t>2025-2026</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>Watford</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>Hull</t>
+        </is>
+      </c>
+      <c r="CE8" s="2" t="n">
+        <v>45927</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1908457</v>
+      </c>
+      <c r="C9" t="n">
+        <v>363718</v>
+      </c>
+      <c r="D9" t="n">
+        <v>27</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Edo Kayembe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>12</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>50</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>90</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>100</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
         <is>
           <t>Oxford</t>
         </is>
       </c>
-      <c r="CE7" s="2" t="n">
+      <c r="CE9" s="2" t="n">
         <v>45934</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1908486</v>
+      </c>
+      <c r="C10" t="n">
+        <v>363718</v>
+      </c>
+      <c r="D10" t="n">
+        <v>27</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Edo Kayembe</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>100</v>
+      </c>
+      <c r="K10" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="L10" t="n">
+        <v>100</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>21</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>50</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>95</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>Sheff Utd</t>
+        </is>
+      </c>
+      <c r="CE10" s="2" t="n">
+        <v>45948</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1908387</v>
+      </c>
+      <c r="C11" t="n">
+        <v>363718</v>
+      </c>
+      <c r="D11" t="n">
+        <v>27</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Edo Kayembe</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>100</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>100</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>WBA</t>
+        </is>
+      </c>
+      <c r="CE11" s="2" t="n">
+        <v>45952</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1908400</v>
+      </c>
+      <c r="C12" t="n">
+        <v>363718</v>
+      </c>
+      <c r="D12" t="n">
+        <v>27</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Edo Kayembe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>91.67</v>
+      </c>
+      <c r="L12" t="n">
+        <v>50</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>17</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.02625</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>100</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="CE12" s="2" t="n">
+        <v>45955</v>
       </c>
     </row>
   </sheetData>
